--- a/public/template/template.xlsx
+++ b/public/template/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Ayodya\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4314C1-C492-46F3-9F06-DFD2B58978F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFC888E-536E-4F82-83E3-D7F6348264C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{1F7556D0-9ACB-435B-BE73-E068EEAFD5C6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>nama_siswa</t>
   </si>
@@ -57,6 +57,24 @@
   </si>
   <si>
     <t>tanggal_lahir</t>
+  </si>
+  <si>
+    <t>TOR4</t>
+  </si>
+  <si>
+    <t>nama</t>
+  </si>
+  <si>
+    <t>Depok</t>
+  </si>
+  <si>
+    <t>1 Januari 2021</t>
+  </si>
+  <si>
+    <t>Ayah</t>
+  </si>
+  <si>
+    <t>cabang1</t>
   </si>
 </sst>
 </file>
@@ -428,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF5EE06D-FA16-4DC9-869C-E4CFC84618B5}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.6328125" customWidth="1"/>
@@ -461,6 +479,29 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
